--- a/resources/Z571/spc_cpk_detail.xlsx
+++ b/resources/Z571/spc_cpk_detail.xlsx
@@ -1859,10 +1859,10 @@
         <v>46201.50052083333</v>
       </c>
       <c r="J28">
-        <v>2.520583691994759</v>
+        <v>2.52058369199476</v>
       </c>
       <c r="K28">
-        <v>2.520583691994759</v>
+        <v>2.52058369199476</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1929,10 +1929,10 @@
         <v>46201.50052083333</v>
       </c>
       <c r="J30">
-        <v>2.520583691994759</v>
+        <v>2.52058369199476</v>
       </c>
       <c r="K30">
-        <v>2.520583691994759</v>
+        <v>2.52058369199476</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2664,10 +2664,10 @@
         <v>46195.76615740741</v>
       </c>
       <c r="J51">
-        <v>5.231814636397818</v>
+        <v>5.23181463639782</v>
       </c>
       <c r="K51">
-        <v>5.231814636397818</v>
+        <v>5.23181463639782</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2833,10 +2833,10 @@
         <v>46205.81633101852</v>
       </c>
       <c r="J56">
-        <v>4.287553245127547</v>
+        <v>4.287553245127548</v>
       </c>
       <c r="K56">
-        <v>4.287553245127547</v>
+        <v>4.287553245127548</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4822,10 +4822,10 @@
         <v>46220.69388888889</v>
       </c>
       <c r="J113">
-        <v>1.700125884327304</v>
+        <v>1.700125884327303</v>
       </c>
       <c r="K113">
-        <v>1.700125884327304</v>
+        <v>1.700125884327303</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -5137,10 +5137,10 @@
         <v>46220.69388888889</v>
       </c>
       <c r="J122">
-        <v>1.700125884327304</v>
+        <v>1.700125884327303</v>
       </c>
       <c r="K122">
-        <v>1.700125884327304</v>
+        <v>1.700125884327303</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5942,10 +5942,10 @@
         <v>46204.47847222222</v>
       </c>
       <c r="J145">
-        <v>1.564016012856579</v>
+        <v>1.564016012856578</v>
       </c>
       <c r="K145">
-        <v>1.564016012856579</v>
+        <v>1.564016012856578</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -6117,10 +6117,10 @@
         <v>46219.91038194444</v>
       </c>
       <c r="J150">
-        <v>1.546617272960087</v>
+        <v>1.546617272960088</v>
       </c>
       <c r="K150">
-        <v>1.546617272960087</v>
+        <v>1.546617272960088</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -7342,10 +7342,10 @@
         <v>46213.27633101852</v>
       </c>
       <c r="J185">
-        <v>1.752946939168391</v>
+        <v>1.752946939168392</v>
       </c>
       <c r="K185">
-        <v>1.752946939168391</v>
+        <v>1.752946939168392</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -8007,10 +8007,10 @@
         <v>46221.75945601852</v>
       </c>
       <c r="J204">
-        <v>1.993908071659143</v>
+        <v>1.993908071659142</v>
       </c>
       <c r="K204">
-        <v>1.993908071659143</v>
+        <v>1.993908071659142</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -9512,10 +9512,10 @@
         <v>46213.99768518518</v>
       </c>
       <c r="J247">
-        <v>2.194646964594397</v>
+        <v>2.194646964594396</v>
       </c>
       <c r="K247">
-        <v>2.194646964594397</v>
+        <v>2.194646964594396</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -10807,10 +10807,10 @@
         <v>46215.46884259259</v>
       </c>
       <c r="J284">
-        <v>2.149285405693324</v>
+        <v>2.149285405693323</v>
       </c>
       <c r="K284">
-        <v>2.149285405693324</v>
+        <v>2.149285405693323</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -11087,10 +11087,10 @@
         <v>46215.46884259259</v>
       </c>
       <c r="J292">
-        <v>1.42119589370879</v>
+        <v>1.421195893708791</v>
       </c>
       <c r="K292">
-        <v>1.42119589370879</v>
+        <v>1.421195893708791</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -12557,10 +12557,10 @@
         <v>46227.24700231481</v>
       </c>
       <c r="J334">
-        <v>2.009448440007816</v>
+        <v>2.009448440007815</v>
       </c>
       <c r="K334">
-        <v>2.009448440007816</v>
+        <v>2.009448440007815</v>
       </c>
     </row>
     <row r="335" spans="1:11">
@@ -12627,10 +12627,10 @@
         <v>46227.24700231481</v>
       </c>
       <c r="J336">
-        <v>1.259597656737996</v>
+        <v>1.259597656737995</v>
       </c>
       <c r="K336">
-        <v>1.259597656737996</v>
+        <v>1.259597656737995</v>
       </c>
     </row>
     <row r="337" spans="1:11">
@@ -15217,10 +15217,10 @@
         <v>46215.58958333333</v>
       </c>
       <c r="J410">
-        <v>1.317015254347833</v>
+        <v>1.317015254347832</v>
       </c>
       <c r="K410">
-        <v>1.317015254347833</v>
+        <v>1.317015254347832</v>
       </c>
     </row>
     <row r="411" spans="1:11">
@@ -15392,10 +15392,10 @@
         <v>46203.91923611111</v>
       </c>
       <c r="J415">
-        <v>1.604473975752033</v>
+        <v>1.604473975752034</v>
       </c>
       <c r="K415">
-        <v>1.604473975752033</v>
+        <v>1.604473975752034</v>
       </c>
     </row>
     <row r="416" spans="1:11">
@@ -15532,10 +15532,10 @@
         <v>46210.93533564815</v>
       </c>
       <c r="J419">
-        <v>0.9499560174895892</v>
+        <v>0.9499560174895891</v>
       </c>
       <c r="K419">
-        <v>0.9499560174895892</v>
+        <v>0.9499560174895891</v>
       </c>
     </row>
     <row r="420" spans="1:11">
@@ -16197,10 +16197,10 @@
         <v>46229.55434027778</v>
       </c>
       <c r="J438">
-        <v>1.645932928441496</v>
+        <v>1.645932928441497</v>
       </c>
       <c r="K438">
-        <v>1.645932928441496</v>
+        <v>1.645932928441497</v>
       </c>
     </row>
     <row r="439" spans="1:11">
@@ -17002,10 +17002,10 @@
         <v>46175.26888888889</v>
       </c>
       <c r="J461">
-        <v>2.15258251437563</v>
+        <v>2.152582514375631</v>
       </c>
       <c r="K461">
-        <v>2.15258251437563</v>
+        <v>2.152582514375631</v>
       </c>
     </row>
     <row r="462" spans="1:11">
@@ -17037,10 +17037,10 @@
         <v>46175.26888888889</v>
       </c>
       <c r="J462">
-        <v>2.15258251437563</v>
+        <v>2.152582514375631</v>
       </c>
       <c r="K462">
-        <v>2.15258251437563</v>
+        <v>2.152582514375631</v>
       </c>
     </row>
     <row r="463" spans="1:11">
@@ -17072,10 +17072,10 @@
         <v>46175.26888888889</v>
       </c>
       <c r="J463">
-        <v>2.15258251437563</v>
+        <v>2.152582514375631</v>
       </c>
       <c r="K463">
-        <v>2.15258251437563</v>
+        <v>2.152582514375631</v>
       </c>
     </row>
     <row r="464" spans="1:11">
@@ -17282,10 +17282,10 @@
         <v>46216.75729166667</v>
       </c>
       <c r="J469">
-        <v>2.823651510215347</v>
+        <v>2.823651510215346</v>
       </c>
       <c r="K469">
-        <v>2.823651510215347</v>
+        <v>2.823651510215346</v>
       </c>
     </row>
     <row r="470" spans="1:11">
@@ -17387,10 +17387,10 @@
         <v>46174.86177083333</v>
       </c>
       <c r="J472">
-        <v>2.380248954699536</v>
+        <v>2.380248954699535</v>
       </c>
       <c r="K472">
-        <v>2.380248954699536</v>
+        <v>2.380248954699535</v>
       </c>
     </row>
     <row r="473" spans="1:11">
@@ -17492,10 +17492,10 @@
         <v>46207.99643518519</v>
       </c>
       <c r="J475">
-        <v>2.59263450081682</v>
+        <v>2.592634500816821</v>
       </c>
       <c r="K475">
-        <v>2.59263450081682</v>
+        <v>2.592634500816821</v>
       </c>
     </row>
     <row r="476" spans="1:11">
@@ -17597,10 +17597,10 @@
         <v>46216.75729166667</v>
       </c>
       <c r="J478">
-        <v>2.823651510215347</v>
+        <v>2.823651510215346</v>
       </c>
       <c r="K478">
-        <v>2.823651510215347</v>
+        <v>2.823651510215346</v>
       </c>
     </row>
     <row r="479" spans="1:11">
@@ -18017,10 +18017,10 @@
         <v>46178.06965277778</v>
       </c>
       <c r="J490">
-        <v>1.887419491654944</v>
+        <v>1.887419491654945</v>
       </c>
       <c r="K490">
-        <v>1.887419491654944</v>
+        <v>1.887419491654945</v>
       </c>
     </row>
     <row r="491" spans="1:11">
@@ -19242,10 +19242,10 @@
         <v>46177.15527777778</v>
       </c>
       <c r="J525">
-        <v>1.373076667919404</v>
+        <v>1.373076667919405</v>
       </c>
       <c r="K525">
-        <v>1.373076667919404</v>
+        <v>1.373076667919405</v>
       </c>
     </row>
     <row r="526" spans="1:11">
@@ -19837,10 +19837,10 @@
         <v>46176.54075231482</v>
       </c>
       <c r="J542">
-        <v>3.956194984743943</v>
+        <v>3.956194984743942</v>
       </c>
       <c r="K542">
-        <v>3.956194984743943</v>
+        <v>3.956194984743942</v>
       </c>
     </row>
     <row r="543" spans="1:11">
@@ -19872,10 +19872,10 @@
         <v>46179.59584490741</v>
       </c>
       <c r="J543">
-        <v>3.633838842478156</v>
+        <v>3.633838842478157</v>
       </c>
       <c r="K543">
-        <v>3.633838842478156</v>
+        <v>3.633838842478157</v>
       </c>
     </row>
     <row r="544" spans="1:11">
@@ -20642,10 +20642,10 @@
         <v>46209.95197916667</v>
       </c>
       <c r="J565">
-        <v>1.592563036649798</v>
+        <v>1.592563036649799</v>
       </c>
       <c r="K565">
-        <v>1.592563036649798</v>
+        <v>1.592563036649799</v>
       </c>
     </row>
     <row r="566" spans="1:11">
@@ -20992,10 +20992,10 @@
         <v>46183.15116898148</v>
       </c>
       <c r="J575">
-        <v>1.462566850258829</v>
+        <v>1.462566850258828</v>
       </c>
       <c r="K575">
-        <v>1.462566850258829</v>
+        <v>1.462566850258828</v>
       </c>
     </row>
     <row r="576" spans="1:11">
@@ -21972,10 +21972,10 @@
         <v>46216.99552083333</v>
       </c>
       <c r="J603">
-        <v>1.484980269406933</v>
+        <v>1.484980269406932</v>
       </c>
       <c r="K603">
-        <v>1.484980269406933</v>
+        <v>1.484980269406932</v>
       </c>
     </row>
     <row r="604" spans="1:11">
@@ -22392,10 +22392,10 @@
         <v>46182.92877314815</v>
       </c>
       <c r="J615">
-        <v>3.59061050255973</v>
+        <v>3.590610502559729</v>
       </c>
       <c r="K615">
-        <v>3.59061050255973</v>
+        <v>3.590610502559729</v>
       </c>
     </row>
     <row r="616" spans="1:11">
@@ -22567,10 +22567,10 @@
         <v>46226.97774305556</v>
       </c>
       <c r="J620">
-        <v>4.217528305734777</v>
+        <v>4.217528305734776</v>
       </c>
       <c r="K620">
-        <v>4.217528305734777</v>
+        <v>4.217528305734776</v>
       </c>
     </row>
     <row r="621" spans="1:11">
@@ -22707,10 +22707,10 @@
         <v>46226.97774305556</v>
       </c>
       <c r="J624">
-        <v>4.217528305734777</v>
+        <v>4.217528305734776</v>
       </c>
       <c r="K624">
-        <v>4.217528305734777</v>
+        <v>4.217528305734776</v>
       </c>
     </row>
     <row r="625" spans="1:11">
@@ -22777,10 +22777,10 @@
         <v>46229.99856481481</v>
       </c>
       <c r="J626">
-        <v>1.323856658327005</v>
+        <v>1.323856658327006</v>
       </c>
       <c r="K626">
-        <v>1.323856658327005</v>
+        <v>1.323856658327006</v>
       </c>
     </row>
     <row r="627" spans="1:11">
@@ -23681,10 +23681,10 @@
         <v>46182.66645833333</v>
       </c>
       <c r="J652">
-        <v>1.480367350588764</v>
+        <v>1.480367350588763</v>
       </c>
       <c r="K652">
-        <v>1.480367350588764</v>
+        <v>1.480367350588763</v>
       </c>
     </row>
     <row r="653" spans="1:11">
@@ -24171,10 +24171,10 @@
         <v>46218.44195601852</v>
       </c>
       <c r="J666">
-        <v>3.73998149982285</v>
+        <v>3.739981499822851</v>
       </c>
       <c r="K666">
-        <v>3.73998149982285</v>
+        <v>3.739981499822851</v>
       </c>
     </row>
     <row r="667" spans="1:11">
@@ -24241,10 +24241,10 @@
         <v>46218.44195601852</v>
       </c>
       <c r="J668">
-        <v>3.73998149982285</v>
+        <v>3.739981499822851</v>
       </c>
       <c r="K668">
-        <v>3.73998149982285</v>
+        <v>3.739981499822851</v>
       </c>
     </row>
     <row r="669" spans="1:11">
@@ -24311,10 +24311,10 @@
         <v>46228.37736111111</v>
       </c>
       <c r="J670">
-        <v>2.175637378683917</v>
+        <v>2.175637378683916</v>
       </c>
       <c r="K670">
-        <v>2.175637378683917</v>
+        <v>2.175637378683916</v>
       </c>
     </row>
     <row r="671" spans="1:11">
@@ -25291,10 +25291,10 @@
         <v>46229.95515046296</v>
       </c>
       <c r="J698">
-        <v>2.428424374447539</v>
+        <v>2.428424374447538</v>
       </c>
       <c r="K698">
-        <v>2.428424374447539</v>
+        <v>2.428424374447538</v>
       </c>
     </row>
     <row r="699" spans="1:11">
@@ -25396,10 +25396,10 @@
         <v>46229.95515046296</v>
       </c>
       <c r="J701">
-        <v>2.428424374447539</v>
+        <v>2.428424374447538</v>
       </c>
       <c r="K701">
-        <v>2.428424374447539</v>
+        <v>2.428424374447538</v>
       </c>
     </row>
     <row r="702" spans="1:11">
@@ -26131,10 +26131,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J722">
-        <v>1.810405069141118</v>
+        <v>2.040900545127396</v>
       </c>
       <c r="K722">
-        <v>1.810405069141118</v>
+        <v>2.040900545127396</v>
       </c>
     </row>
     <row r="723" spans="1:11">
@@ -26236,10 +26236,10 @@
         <v>46218.0903125</v>
       </c>
       <c r="J725">
-        <v>2.285479925728788</v>
+        <v>2.285479925728787</v>
       </c>
       <c r="K725">
-        <v>2.285479925728788</v>
+        <v>2.285479925728787</v>
       </c>
     </row>
     <row r="726" spans="1:11">
@@ -26271,10 +26271,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J726">
-        <v>1.710138798502391</v>
+        <v>1.952157839845969</v>
       </c>
       <c r="K726">
-        <v>1.710138798502391</v>
+        <v>1.952157839845969</v>
       </c>
     </row>
     <row r="727" spans="1:11">
@@ -26411,10 +26411,10 @@
         <v>46218.0903125</v>
       </c>
       <c r="J730">
-        <v>2.285479925728788</v>
+        <v>2.285479925728787</v>
       </c>
       <c r="K730">
-        <v>2.285479925728788</v>
+        <v>2.285479925728787</v>
       </c>
     </row>
     <row r="731" spans="1:11">
@@ -26481,10 +26481,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J732">
-        <v>1.585341740011126</v>
+        <v>1.856030972354771</v>
       </c>
       <c r="K732">
-        <v>1.585341740011126</v>
+        <v>1.856030972354771</v>
       </c>
     </row>
     <row r="733" spans="1:11">
@@ -26936,10 +26936,10 @@
         <v>46186.87597222222</v>
       </c>
       <c r="J745">
-        <v>2.52564900501953</v>
+        <v>2.525649005019531</v>
       </c>
       <c r="K745">
-        <v>2.52564900501953</v>
+        <v>2.525649005019531</v>
       </c>
     </row>
     <row r="746" spans="1:11">
@@ -26971,10 +26971,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J746">
-        <v>1.807483735442206</v>
+        <v>2.097563028332512</v>
       </c>
       <c r="K746">
-        <v>1.971722188640257</v>
+        <v>2.097563028332512</v>
       </c>
     </row>
     <row r="747" spans="1:11">
@@ -27006,10 +27006,10 @@
         <v>46186.87597222222</v>
       </c>
       <c r="J747">
-        <v>2.52564900501953</v>
+        <v>2.525649005019531</v>
       </c>
       <c r="K747">
-        <v>2.52564900501953</v>
+        <v>2.525649005019531</v>
       </c>
     </row>
     <row r="748" spans="1:11">
@@ -27111,10 +27111,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J750">
-        <v>1.596784037017879</v>
+        <v>1.996053088893404</v>
       </c>
       <c r="K750">
-        <v>1.811872300167577</v>
+        <v>1.996053088893404</v>
       </c>
     </row>
     <row r="751" spans="1:11">
@@ -27181,10 +27181,10 @@
         <v>46186.87597222222</v>
       </c>
       <c r="J752">
-        <v>2.440675317702928</v>
+        <v>2.440675317702927</v>
       </c>
       <c r="K752">
-        <v>2.440675317702928</v>
+        <v>2.440675317702927</v>
       </c>
     </row>
     <row r="753" spans="1:11">
@@ -27321,10 +27321,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J756">
-        <v>1.49002630549511</v>
+        <v>2.039530750769926</v>
       </c>
       <c r="K756">
-        <v>1.766159059376935</v>
+        <v>2.039530750769926</v>
       </c>
     </row>
     <row r="757" spans="1:11">
@@ -27391,10 +27391,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J758">
-        <v>1.582976299915201</v>
+        <v>1.69512926462883</v>
       </c>
       <c r="K758">
-        <v>1.672133665706888</v>
+        <v>1.69512926462883</v>
       </c>
     </row>
     <row r="759" spans="1:11">
@@ -27461,10 +27461,10 @@
         <v>46214.13641203703</v>
       </c>
       <c r="J760">
-        <v>1.446550781588233</v>
+        <v>1.446550781588232</v>
       </c>
       <c r="K760">
-        <v>1.446550781588233</v>
+        <v>1.446550781588232</v>
       </c>
     </row>
     <row r="761" spans="1:11">
@@ -27531,10 +27531,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J762">
-        <v>1.69644782799073</v>
+        <v>1.950245963986431</v>
       </c>
       <c r="K762">
-        <v>1.894201822557383</v>
+        <v>1.950245963986431</v>
       </c>
     </row>
     <row r="763" spans="1:11">
@@ -27636,10 +27636,10 @@
         <v>46214.13641203703</v>
       </c>
       <c r="J765">
-        <v>1.446550781588233</v>
+        <v>1.446550781588232</v>
       </c>
       <c r="K765">
-        <v>1.446550781588233</v>
+        <v>1.446550781588232</v>
       </c>
     </row>
     <row r="766" spans="1:11">
@@ -27741,10 +27741,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J768">
-        <v>1.617401994336092</v>
+        <v>1.967681102990148</v>
       </c>
       <c r="K768">
-        <v>1.887551180663596</v>
+        <v>1.967681102990148</v>
       </c>
     </row>
     <row r="769" spans="1:11">
@@ -27811,10 +27811,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J770">
-        <v>1.944821888415452</v>
+        <v>2.031351164836437</v>
       </c>
       <c r="K770">
-        <v>1.944821888415452</v>
+        <v>2.031351164836437</v>
       </c>
     </row>
     <row r="771" spans="1:11">
@@ -27951,10 +27951,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J774">
-        <v>1.864144922596317</v>
+        <v>1.998238979613067</v>
       </c>
       <c r="K774">
-        <v>1.864144922596317</v>
+        <v>1.998238979613067</v>
       </c>
     </row>
     <row r="775" spans="1:11">
@@ -28161,10 +28161,10 @@
         <v>46229.58684027778</v>
       </c>
       <c r="J780">
-        <v>1.753539389783329</v>
+        <v>1.91203417838951</v>
       </c>
       <c r="K780">
-        <v>1.753539389783329</v>
+        <v>1.91203417838951</v>
       </c>
     </row>
     <row r="781" spans="1:11">
@@ -29246,10 +29246,10 @@
         <v>46185.7097337963</v>
       </c>
       <c r="J811">
-        <v>2.200494585818136</v>
+        <v>2.200494585818135</v>
       </c>
       <c r="K811">
-        <v>2.200494585818136</v>
+        <v>2.200494585818135</v>
       </c>
     </row>
     <row r="812" spans="1:11">
@@ -30961,10 +30961,10 @@
         <v>46225.72084490741</v>
       </c>
       <c r="J860">
-        <v>2.211150895111773</v>
+        <v>2.211150895111772</v>
       </c>
       <c r="K860">
-        <v>2.211150895111773</v>
+        <v>2.211150895111772</v>
       </c>
     </row>
     <row r="861" spans="1:11">
@@ -31031,10 +31031,10 @@
         <v>46175.438125</v>
       </c>
       <c r="J862">
-        <v>2.13421714900299</v>
+        <v>2.134217149002989</v>
       </c>
       <c r="K862">
-        <v>2.13421714900299</v>
+        <v>2.134217149002989</v>
       </c>
     </row>
     <row r="863" spans="1:11">
@@ -31206,10 +31206,10 @@
         <v>46225.72084490741</v>
       </c>
       <c r="J867">
-        <v>2.211150895111773</v>
+        <v>2.211150895111772</v>
       </c>
       <c r="K867">
-        <v>2.211150895111773</v>
+        <v>2.211150895111772</v>
       </c>
     </row>
     <row r="868" spans="1:11">
@@ -32711,10 +32711,10 @@
         <v>46210.26637731482</v>
       </c>
       <c r="J910">
-        <v>1.322743322795231</v>
+        <v>1.322743322795232</v>
       </c>
       <c r="K910">
-        <v>1.322743322795231</v>
+        <v>1.322743322795232</v>
       </c>
     </row>
     <row r="911" spans="1:11">
@@ -33306,10 +33306,10 @@
         <v>46212.38128472222</v>
       </c>
       <c r="J927">
-        <v>0.9342739104821057</v>
+        <v>0.9342739104821061</v>
       </c>
       <c r="K927">
-        <v>0.9342739104821057</v>
+        <v>0.9342739104821061</v>
       </c>
     </row>
     <row r="928" spans="1:11">
@@ -33936,10 +33936,10 @@
         <v>46215.27032407407</v>
       </c>
       <c r="J945">
-        <v>1.72472679991808</v>
+        <v>1.724726799918081</v>
       </c>
       <c r="K945">
-        <v>1.72472679991808</v>
+        <v>1.724726799918081</v>
       </c>
     </row>
     <row r="946" spans="1:11">
@@ -35546,10 +35546,10 @@
         <v>46208.7921412037</v>
       </c>
       <c r="J991">
-        <v>0.9893525440954595</v>
+        <v>0.9893525440954594</v>
       </c>
       <c r="K991">
-        <v>0.9893525440954595</v>
+        <v>0.9893525440954594</v>
       </c>
     </row>
     <row r="992" spans="1:11">
@@ -35721,10 +35721,10 @@
         <v>46196.86282407407</v>
       </c>
       <c r="J996">
-        <v>4.289618217496974</v>
+        <v>4.289618217496975</v>
       </c>
       <c r="K996">
-        <v>4.289618217496974</v>
+        <v>4.289618217496975</v>
       </c>
     </row>
     <row r="997" spans="1:11">
@@ -35966,10 +35966,10 @@
         <v>46209.59442129629</v>
       </c>
       <c r="J1003">
-        <v>5.032474135585299</v>
+        <v>5.0324741355853</v>
       </c>
       <c r="K1003">
-        <v>5.032474135585299</v>
+        <v>5.0324741355853</v>
       </c>
     </row>
     <row r="1004" spans="1:11">
@@ -36911,10 +36911,10 @@
         <v>46222.83075231482</v>
       </c>
       <c r="J1030">
-        <v>2.52205170391284</v>
+        <v>2.522051703912841</v>
       </c>
       <c r="K1030">
-        <v>2.52205170391284</v>
+        <v>2.522051703912841</v>
       </c>
     </row>
     <row r="1031" spans="1:11">
@@ -37261,10 +37261,10 @@
         <v>46229.3266087963</v>
       </c>
       <c r="J1040">
-        <v>2.343002274652185</v>
+        <v>2.343002274652184</v>
       </c>
       <c r="K1040">
-        <v>2.343002274652185</v>
+        <v>2.343002274652184</v>
       </c>
     </row>
     <row r="1041" spans="1:11">
@@ -37506,10 +37506,10 @@
         <v>46209.09982638889</v>
       </c>
       <c r="J1047">
-        <v>1.435978807862337</v>
+        <v>1.435978807862336</v>
       </c>
       <c r="K1047">
-        <v>1.435978807862337</v>
+        <v>1.435978807862336</v>
       </c>
     </row>
     <row r="1048" spans="1:11">
@@ -38031,10 +38031,10 @@
         <v>46213.51275462963</v>
       </c>
       <c r="J1062">
-        <v>1.094183419468239</v>
+        <v>1.094183419468238</v>
       </c>
       <c r="K1062">
-        <v>1.094183419468239</v>
+        <v>1.094183419468238</v>
       </c>
     </row>
     <row r="1063" spans="1:11">
@@ -38171,10 +38171,10 @@
         <v>46224.28636574074</v>
       </c>
       <c r="J1066">
-        <v>0.8807525678523676</v>
+        <v>0.8807525678523674</v>
       </c>
       <c r="K1066">
-        <v>0.8807525678523676</v>
+        <v>0.8807525678523674</v>
       </c>
     </row>
     <row r="1067" spans="1:11">
@@ -38626,10 +38626,10 @@
         <v>46190.91314814815</v>
       </c>
       <c r="J1079">
-        <v>2.853785525602939</v>
+        <v>2.853785525602938</v>
       </c>
       <c r="K1079">
-        <v>2.853785525602939</v>
+        <v>2.853785525602938</v>
       </c>
     </row>
     <row r="1080" spans="1:11">
@@ -38941,10 +38941,10 @@
         <v>46221.91496527778</v>
       </c>
       <c r="J1088">
-        <v>3.646439923132819</v>
+        <v>3.646439923132818</v>
       </c>
       <c r="K1088">
-        <v>3.646439923132819</v>
+        <v>3.646439923132818</v>
       </c>
     </row>
     <row r="1089" spans="1:11">
@@ -39081,10 +39081,10 @@
         <v>46182.09953703704</v>
       </c>
       <c r="J1092">
-        <v>1.493753000500821</v>
+        <v>1.49375300050082</v>
       </c>
       <c r="K1092">
-        <v>1.493753000500821</v>
+        <v>1.49375300050082</v>
       </c>
     </row>
     <row r="1093" spans="1:11">
@@ -39326,10 +39326,10 @@
         <v>46189.91048611111</v>
       </c>
       <c r="J1099">
-        <v>3.235944693356416</v>
+        <v>3.235944693356415</v>
       </c>
       <c r="K1099">
-        <v>3.235944693356416</v>
+        <v>3.235944693356415</v>
       </c>
     </row>
     <row r="1100" spans="1:11">
@@ -39781,10 +39781,10 @@
         <v>46222.0265162037</v>
       </c>
       <c r="J1112">
-        <v>2.587722487662592</v>
+        <v>2.587722487662593</v>
       </c>
       <c r="K1112">
-        <v>2.587722487662592</v>
+        <v>2.587722487662593</v>
       </c>
     </row>
     <row r="1113" spans="1:11">
@@ -39816,10 +39816,10 @@
         <v>46182.09953703704</v>
       </c>
       <c r="J1113">
-        <v>1.207218044700374</v>
+        <v>1.207218044700375</v>
       </c>
       <c r="K1113">
-        <v>1.207218044700374</v>
+        <v>1.207218044700375</v>
       </c>
     </row>
     <row r="1114" spans="1:11">
@@ -39956,10 +39956,10 @@
         <v>46181.65299768518</v>
       </c>
       <c r="J1117">
-        <v>1.117006258461609</v>
+        <v>1.117006258461611</v>
       </c>
       <c r="K1117">
-        <v>1.117006258461609</v>
+        <v>1.117006258461611</v>
       </c>
     </row>
     <row r="1118" spans="1:11">
@@ -40376,10 +40376,10 @@
         <v>46220.93282407407</v>
       </c>
       <c r="J1129">
-        <v>2.185704367559678</v>
+        <v>2.18570436755968</v>
       </c>
       <c r="K1129">
-        <v>2.185704367559678</v>
+        <v>2.18570436755968</v>
       </c>
     </row>
     <row r="1130" spans="1:11">
@@ -40481,10 +40481,10 @@
         <v>46203.9737037037</v>
       </c>
       <c r="J1132">
-        <v>3.252609079706018</v>
+        <v>3.252609079706017</v>
       </c>
       <c r="K1132">
-        <v>3.252609079706018</v>
+        <v>3.252609079706017</v>
       </c>
     </row>
     <row r="1133" spans="1:11">
@@ -40796,10 +40796,10 @@
         <v>46189.91048611111</v>
       </c>
       <c r="J1141">
-        <v>5.271882587050079</v>
+        <v>5.271882587050077</v>
       </c>
       <c r="K1141">
-        <v>5.271882587050079</v>
+        <v>5.271882587050077</v>
       </c>
     </row>
     <row r="1142" spans="1:11">
@@ -41461,10 +41461,10 @@
         <v>46182.09953703704</v>
       </c>
       <c r="J1160">
-        <v>2.978328304688875</v>
+        <v>2.978328304688876</v>
       </c>
       <c r="K1160">
-        <v>2.978328304688875</v>
+        <v>2.978328304688876</v>
       </c>
     </row>
     <row r="1161" spans="1:11">
@@ -41601,10 +41601,10 @@
         <v>46203.9737037037</v>
       </c>
       <c r="J1164">
-        <v>2.864113025355024</v>
+        <v>2.864113025355025</v>
       </c>
       <c r="K1164">
-        <v>2.864113025355024</v>
+        <v>2.864113025355025</v>
       </c>
     </row>
     <row r="1165" spans="1:11">
@@ -41706,10 +41706,10 @@
         <v>46216.93078703704</v>
       </c>
       <c r="J1167">
-        <v>2.441187302979422</v>
+        <v>2.441187302979423</v>
       </c>
       <c r="K1167">
-        <v>2.441187302979422</v>
+        <v>2.441187302979423</v>
       </c>
     </row>
     <row r="1168" spans="1:11">
@@ -42406,10 +42406,10 @@
         <v>46205.60184027778</v>
       </c>
       <c r="J1187">
-        <v>6.999844657339267</v>
+        <v>6.999844657339269</v>
       </c>
       <c r="K1187">
-        <v>6.999844657339267</v>
+        <v>6.999844657339269</v>
       </c>
     </row>
     <row r="1188" spans="1:11">
@@ -42476,10 +42476,10 @@
         <v>46217.93251157407</v>
       </c>
       <c r="J1189">
-        <v>2.830012494608551</v>
+        <v>2.830012494608552</v>
       </c>
       <c r="K1189">
-        <v>2.830012494608551</v>
+        <v>2.830012494608552</v>
       </c>
     </row>
     <row r="1190" spans="1:11">
@@ -42721,10 +42721,10 @@
         <v>46221.92895833333</v>
       </c>
       <c r="J1196">
-        <v>3.438148556176436</v>
+        <v>3.438148556176435</v>
       </c>
       <c r="K1196">
-        <v>3.438148556176436</v>
+        <v>3.438148556176435</v>
       </c>
     </row>
     <row r="1197" spans="1:11">
@@ -45031,10 +45031,10 @@
         <v>46188.99912037037</v>
       </c>
       <c r="J1262">
-        <v>3.422246641950994</v>
+        <v>3.422246641950993</v>
       </c>
       <c r="K1262">
-        <v>3.422246641950994</v>
+        <v>3.422246641950993</v>
       </c>
     </row>
     <row r="1263" spans="1:11">
@@ -45661,10 +45661,10 @@
         <v>46221.92893518518</v>
       </c>
       <c r="J1280">
-        <v>2.260104981299983</v>
+        <v>2.260104981299984</v>
       </c>
       <c r="K1280">
-        <v>2.260104981299983</v>
+        <v>2.260104981299984</v>
       </c>
     </row>
     <row r="1281" spans="1:11">
@@ -46711,10 +46711,10 @@
         <v>46223.07759259259</v>
       </c>
       <c r="J1310">
-        <v>1.648717080842869</v>
+        <v>1.648717080842868</v>
       </c>
       <c r="K1310">
-        <v>1.648717080842869</v>
+        <v>1.648717080842868</v>
       </c>
     </row>
     <row r="1311" spans="1:11">
@@ -47271,10 +47271,10 @@
         <v>46191.4728125</v>
       </c>
       <c r="J1326">
-        <v>1.344684014186342</v>
+        <v>1.344684014186343</v>
       </c>
       <c r="K1326">
-        <v>1.344684014186342</v>
+        <v>1.344684014186343</v>
       </c>
     </row>
     <row r="1327" spans="1:11">
@@ -47341,10 +47341,10 @@
         <v>46191.4728125</v>
       </c>
       <c r="J1328">
-        <v>1.344684014186342</v>
+        <v>1.344684014186343</v>
       </c>
       <c r="K1328">
-        <v>1.344684014186342</v>
+        <v>1.344684014186343</v>
       </c>
     </row>
     <row r="1329" spans="1:11">
@@ -47411,10 +47411,10 @@
         <v>46221.96019675926</v>
       </c>
       <c r="J1330">
-        <v>1.744753524318051</v>
+        <v>1.74475352431805</v>
       </c>
       <c r="K1330">
-        <v>1.744753524318051</v>
+        <v>1.74475352431805</v>
       </c>
     </row>
     <row r="1331" spans="1:11">
@@ -47481,10 +47481,10 @@
         <v>46191.4728125</v>
       </c>
       <c r="J1332">
-        <v>1.344684014186342</v>
+        <v>1.344684014186343</v>
       </c>
       <c r="K1332">
-        <v>1.344684014186342</v>
+        <v>1.344684014186343</v>
       </c>
     </row>
     <row r="1333" spans="1:11">
@@ -47551,10 +47551,10 @@
         <v>46221.96019675926</v>
       </c>
       <c r="J1334">
-        <v>1.744753524318051</v>
+        <v>1.74475352431805</v>
       </c>
       <c r="K1334">
-        <v>1.744753524318051</v>
+        <v>1.74475352431805</v>
       </c>
     </row>
     <row r="1335" spans="1:11">
@@ -47971,10 +47971,10 @@
         <v>46194.63263888889</v>
       </c>
       <c r="J1346">
-        <v>1.479021612340454</v>
+        <v>1.479021612340453</v>
       </c>
       <c r="K1346">
-        <v>1.479021612340454</v>
+        <v>1.479021612340453</v>
       </c>
     </row>
     <row r="1347" spans="1:11">
@@ -48041,10 +48041,10 @@
         <v>46194.63263888889</v>
       </c>
       <c r="J1348">
-        <v>1.479021612340454</v>
+        <v>1.479021612340453</v>
       </c>
       <c r="K1348">
-        <v>1.479021612340454</v>
+        <v>1.479021612340453</v>
       </c>
     </row>
     <row r="1349" spans="1:11">
@@ -48076,10 +48076,10 @@
         <v>46207.65903935185</v>
       </c>
       <c r="J1349">
-        <v>1.423479755578247</v>
+        <v>1.423479755578248</v>
       </c>
       <c r="K1349">
-        <v>1.423479755578247</v>
+        <v>1.423479755578248</v>
       </c>
     </row>
     <row r="1350" spans="1:11">
@@ -48286,10 +48286,10 @@
         <v>46207.65903935185</v>
       </c>
       <c r="J1355">
-        <v>1.423479755578247</v>
+        <v>1.423479755578248</v>
       </c>
       <c r="K1355">
-        <v>1.423479755578247</v>
+        <v>1.423479755578248</v>
       </c>
     </row>
     <row r="1356" spans="1:11">
@@ -48846,10 +48846,10 @@
         <v>46193.89229166666</v>
       </c>
       <c r="J1371">
-        <v>2.696821469286366</v>
+        <v>2.696821469286365</v>
       </c>
       <c r="K1371">
-        <v>2.696821469286366</v>
+        <v>2.696821469286365</v>
       </c>
     </row>
     <row r="1372" spans="1:11">
@@ -49931,10 +49931,10 @@
         <v>46191.68599537037</v>
       </c>
       <c r="J1402">
-        <v>2.400657745009868</v>
+        <v>2.400657745009869</v>
       </c>
       <c r="K1402">
-        <v>2.400657745009868</v>
+        <v>2.400657745009869</v>
       </c>
     </row>
     <row r="1403" spans="1:11">
@@ -50071,10 +50071,10 @@
         <v>46208.8434375</v>
       </c>
       <c r="J1406">
-        <v>2.5305411959185</v>
+        <v>2.530541195918499</v>
       </c>
       <c r="K1406">
-        <v>2.5305411959185</v>
+        <v>2.530541195918499</v>
       </c>
     </row>
     <row r="1407" spans="1:11">
@@ -50911,10 +50911,10 @@
         <v>46223.11899305556</v>
       </c>
       <c r="J1430">
-        <v>1.367179113389847</v>
+        <v>1.367179113389848</v>
       </c>
       <c r="K1430">
-        <v>1.367179113389847</v>
+        <v>1.367179113389848</v>
       </c>
     </row>
     <row r="1431" spans="1:11">
@@ -51821,10 +51821,10 @@
         <v>46194.77258101852</v>
       </c>
       <c r="J1456">
-        <v>2.821978758406432</v>
+        <v>2.821978758406431</v>
       </c>
       <c r="K1456">
-        <v>2.821978758406432</v>
+        <v>2.821978758406431</v>
       </c>
     </row>
     <row r="1457" spans="1:11">
@@ -51856,10 +51856,10 @@
         <v>46194.77258101852</v>
       </c>
       <c r="J1457">
-        <v>2.821978758406432</v>
+        <v>2.821978758406431</v>
       </c>
       <c r="K1457">
-        <v>2.821978758406432</v>
+        <v>2.821978758406431</v>
       </c>
     </row>
     <row r="1458" spans="1:11">
